--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -88,27 +88,30 @@
     <t>MORA</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CHONKOA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -118,27 +121,30 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
@@ -148,25 +154,25 @@
     <t>MARISOL</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>CRISTIAN LEOBARDO</t>
+  </si>
+  <si>
     <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
   </si>
 </sst>
 </file>
@@ -941,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -979,10 +985,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1002,10 +1008,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1025,10 +1031,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1042,16 +1048,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920111</v>
+        <v>20330051920152</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1071,10 +1077,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1094,10 +1100,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1117,10 +1123,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1140,10 +1146,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1163,10 +1169,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1186,10 +1192,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1198,6 +1204,29 @@
         <v>11</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -85,88 +85,136 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CHONKOA</t>
+  </si>
+  <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
     <t>GILES</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
     <t>SAUL AZAEL</t>
   </si>
   <si>
+    <t>ESTEPHANY SOPHIA</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>EVIAN ISSAIAS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
     <t>MARISOL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
   </si>
   <si>
     <t>CRISTIAN LEOBARDO</t>
@@ -716,16 +764,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>23</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>67.65000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -739,16 +790,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>22</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>64.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -762,16 +816,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>14</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>53.85</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -785,16 +842,19 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +919,7 @@
         <v>67.65000000000001</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -885,7 +945,7 @@
         <v>64.70999999999999</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -911,7 +971,7 @@
         <v>53.85</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -937,7 +997,7 @@
         <v>60</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -985,10 +1045,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1008,10 +1068,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1025,16 +1085,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920217</v>
+        <v>22330051920362</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1048,22 +1108,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920152</v>
+        <v>22330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1071,137 +1131,137 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920006</v>
+        <v>22330051920215</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920011</v>
+        <v>21330051920119</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920017</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920393</v>
+        <v>21330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920394</v>
+        <v>21330051920133</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920229</v>
+        <v>22330051920006</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1209,24 +1269,185 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
+        <v>22330051920011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920017</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920393</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920394</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920217</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920229</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>21330051920111</v>
       </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
         <v>12</v>
       </c>
-      <c r="G12">
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920152</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -88,45 +91,39 @@
     <t>ALFONSO</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>CHONKOA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -136,18 +133,12 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -172,6 +163,9 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
     <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
-    <t>LILIANA</t>
-  </si>
-  <si>
     <t>EVIAN ISSAIAS</t>
   </si>
   <si>
@@ -196,13 +187,7 @@
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
     <t>EDER</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
   </si>
   <si>
     <t>LUIS</t>
@@ -1007,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,16 +1024,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920013</v>
+        <v>22330051920011</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1062,16 +1047,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920026</v>
+        <v>22330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1085,22 +1070,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920362</v>
+        <v>22330051920026</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1108,16 +1093,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920213</v>
+        <v>22330051920362</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1137,10 +1122,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1160,10 +1145,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1183,10 +1168,10 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1206,10 +1191,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1223,39 +1208,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920133</v>
+        <v>22330051920006</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920006</v>
+        <v>22330051920017</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1269,22 +1254,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920011</v>
+        <v>22330051920393</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1292,22 +1277,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920017</v>
+        <v>22330051920394</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1315,16 +1300,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920393</v>
+        <v>22330051920217</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1338,16 +1323,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920394</v>
+        <v>22330051920229</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1361,22 +1346,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920217</v>
+        <v>21330051920111</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1384,70 +1369,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920229</v>
+        <v>20330051920152</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920111</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920152</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
     <t>DIAZ</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>GILES</t>
   </si>
   <si>
@@ -167,6 +173,9 @@
   </si>
   <si>
     <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
   </si>
   <si>
     <t>SAUL AZAEL</t>
@@ -992,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1030,10 +1039,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1053,10 +1062,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1070,16 +1079,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920026</v>
+        <v>22330051920322</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1093,22 +1102,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920362</v>
+        <v>22330051920026</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1116,16 +1125,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920215</v>
+        <v>22330051920362</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1139,22 +1148,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920119</v>
+        <v>22330051920215</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1162,16 +1171,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920125</v>
+        <v>21330051920119</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1185,16 +1194,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920126</v>
+        <v>21330051920125</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1208,7 +1217,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920006</v>
+        <v>21330051920126</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1217,30 +1226,30 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920017</v>
+        <v>22330051920006</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1254,22 +1263,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920393</v>
+        <v>22330051920017</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1277,16 +1286,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920394</v>
+        <v>22330051920393</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1300,16 +1309,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920217</v>
+        <v>22330051920394</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1323,16 +1332,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920229</v>
+        <v>22330051920217</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1346,22 +1355,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920111</v>
+        <v>22330051920229</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1369,16 +1378,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920152</v>
+        <v>21330051920111</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1387,6 +1396,29 @@
         <v>12</v>
       </c>
       <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920152</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>GILES</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -179,9 +173,6 @@
   </si>
   <si>
     <t>SAUL AZAEL</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
     <t>EVIAN ISSAIAS</t>
@@ -1001,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,10 +1030,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1062,10 +1053,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1085,10 +1076,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1108,10 +1099,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1125,16 +1116,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920362</v>
+        <v>22330051920215</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1148,22 +1139,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920215</v>
+        <v>21330051920119</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1171,16 +1162,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920119</v>
+        <v>21330051920125</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1194,16 +1185,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1217,7 +1208,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920126</v>
+        <v>22330051920006</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1226,30 +1217,30 @@
         <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920006</v>
+        <v>22330051920017</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1263,22 +1254,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920017</v>
+        <v>22330051920393</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1286,16 +1277,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920393</v>
+        <v>22330051920394</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1309,16 +1300,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920394</v>
+        <v>22330051920217</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1332,16 +1323,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920217</v>
+        <v>22330051920229</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1355,22 +1346,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920229</v>
+        <v>21330051920111</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1378,16 +1369,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920111</v>
+        <v>20330051920152</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1396,29 +1387,6 @@
         <v>12</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920152</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,133 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>SAUL AZAEL</t>
-  </si>
-  <si>
-    <t>EVIAN ISSAIAS</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
     <t>ZABDIEL</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
     <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
   </si>
 </sst>
 </file>
@@ -606,19 +495,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,19 +521,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>64.70999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -658,19 +547,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>53.85</v>
+        <v>80.77</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -684,10 +573,10 @@
         <v>15</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>6</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -696,7 +585,7 @@
         <v>60</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -749,19 +638,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>67.65000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -775,19 +664,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>64.70999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -801,19 +690,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>53.85</v>
+        <v>69.23</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -827,19 +716,19 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>93.33</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -892,19 +781,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>67.65000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -918,19 +807,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>64.70999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -944,19 +833,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>53.85</v>
+        <v>69.23</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -970,19 +859,19 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>93.33</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,369 +913,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920011</v>
+        <v>21330051920125</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920013</v>
+        <v>20330051920152</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920322</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920026</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920215</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920119</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920125</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920126</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920006</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920017</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920393</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920394</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920217</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920229</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920152</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -784,13 +784,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
         <v>8.1</v>
@@ -810,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H3">
         <v>8.199999999999999</v>
@@ -836,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -862,16 +862,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
   </si>
   <si>
     <t>ZABDIEL</t>
@@ -881,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -913,16 +922,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920125</v>
+        <v>21330051920133</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -931,21 +940,21 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -954,6 +963,29 @@
         <v>12</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920152</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
   </si>
   <si>
     <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>CESAR DANIEL</t>
@@ -890,7 +899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,22 +931,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920133</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -945,16 +954,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920125</v>
+        <v>21330051920133</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -963,21 +972,21 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -986,6 +995,29 @@
         <v>12</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920152</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -82,37 +82,58 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>COYOHUA</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
     <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -899,7 +920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -937,10 +958,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -954,22 +975,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920133</v>
+        <v>22330051920213</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -977,16 +998,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920125</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -995,21 +1016,21 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920152</v>
+        <v>21330051920127</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1018,6 +1039,75 @@
         <v>12</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920125</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>MONT</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -106,12 +109,12 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>BRAVO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
   </si>
   <si>
     <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>ZABDIEL</t>
@@ -920,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,10 +964,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,10 +987,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1004,10 +1010,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1030,7 +1036,7 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1044,7 +1050,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920125</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1053,30 +1059,30 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920152</v>
+        <v>21330051920125</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1090,16 +1096,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920133</v>
+        <v>20330051920152</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1108,6 +1114,29 @@
         <v>12</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
